--- a/TP MOGUANGUE Auguste Arcel_Master1 IG_ Analyse Donnees.xlsx
+++ b/TP MOGUANGUE Auguste Arcel_Master1 IG_ Analyse Donnees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m50056592\Desktop\A1_RAPPORT_MSSD_Auguste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1C1244F-0A55-4C94-A754-EA681FF354A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B34F1A-A2B4-4580-8063-4A20C6752036}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{281EA207-E3DD-430C-9B26-BCB098450AD4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="vente annuelle des produits " sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'vente annuelle des produits '!$A$4:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'vente annuelle des produits '!$A$7:$I$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -321,7 +321,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4</c:f>
+              <c:f>'vente annuelle des produits '!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -354,7 +354,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$B$3:$K$3</c:f>
+              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -389,7 +389,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$B$4:$K$4</c:f>
+              <c:f>'vente annuelle des produits '!$B$7:$K$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -434,7 +434,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$5</c:f>
+              <c:f>'vente annuelle des produits '!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -467,7 +467,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$B$3:$K$3</c:f>
+              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -502,7 +502,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$B$5:$K$5</c:f>
+              <c:f>'vente annuelle des produits '!$B$8:$K$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -547,7 +547,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$6</c:f>
+              <c:f>'vente annuelle des produits '!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -580,7 +580,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$B$3:$K$3</c:f>
+              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -615,7 +615,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
+              <c:f>'vente annuelle des produits '!$B$9:$K$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -660,7 +660,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -693,7 +693,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$B$3:$K$3</c:f>
+              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -728,7 +728,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$B$7:$K$7</c:f>
+              <c:f>'vente annuelle des produits '!$B$10:$K$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1057,7 +1057,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4</c:f>
+              <c:f>'vente annuelle des produits '!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1086,7 +1086,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$B$3:$K$3</c:f>
+              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -1121,7 +1121,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$B$4:$K$4</c:f>
+              <c:f>'vente annuelle des produits '!$B$7:$K$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1167,7 +1167,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$5</c:f>
+              <c:f>'vente annuelle des produits '!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1196,7 +1196,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$B$3:$K$3</c:f>
+              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -1231,7 +1231,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$B$5:$K$5</c:f>
+              <c:f>'vente annuelle des produits '!$B$8:$K$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1277,7 +1277,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$6</c:f>
+              <c:f>'vente annuelle des produits '!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1306,7 +1306,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$B$3:$K$3</c:f>
+              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -1341,7 +1341,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
+              <c:f>'vente annuelle des produits '!$B$9:$K$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1387,7 +1387,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1416,7 +1416,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$B$3:$K$3</c:f>
+              <c:f>'vente annuelle des produits '!$B$6:$K$6</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -1451,7 +1451,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$B$7:$K$7</c:f>
+              <c:f>'vente annuelle des produits '!$B$10:$K$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1793,7 +1793,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$B$3</c:f>
+              <c:f>'vente annuelle des produits '!$B$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1970,7 +1970,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4:$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$7:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1990,7 +1990,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$B$4:$B$7</c:f>
+              <c:f>'vente annuelle des produits '!$B$7:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2020,7 +2020,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$C$3</c:f>
+              <c:f>'vente annuelle des produits '!$C$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2197,7 +2197,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4:$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$7:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -2217,7 +2217,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$C$4:$C$7</c:f>
+              <c:f>'vente annuelle des produits '!$C$7:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2247,7 +2247,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$D$3</c:f>
+              <c:f>'vente annuelle des produits '!$D$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2424,7 +2424,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4:$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$7:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -2444,7 +2444,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$D$4:$D$7</c:f>
+              <c:f>'vente annuelle des produits '!$D$7:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2474,7 +2474,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$E$3</c:f>
+              <c:f>'vente annuelle des produits '!$E$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2651,7 +2651,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4:$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$7:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -2671,7 +2671,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$E$4:$E$7</c:f>
+              <c:f>'vente annuelle des produits '!$E$7:$E$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2701,7 +2701,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$F$3</c:f>
+              <c:f>'vente annuelle des produits '!$F$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2878,7 +2878,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4:$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$7:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -2898,7 +2898,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$F$4:$F$7</c:f>
+              <c:f>'vente annuelle des produits '!$F$7:$F$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2928,7 +2928,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$G$3</c:f>
+              <c:f>'vente annuelle des produits '!$G$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3105,7 +3105,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4:$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$7:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -3125,7 +3125,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$G$4:$G$7</c:f>
+              <c:f>'vente annuelle des produits '!$G$7:$G$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3155,7 +3155,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$H$3</c:f>
+              <c:f>'vente annuelle des produits '!$H$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3332,7 +3332,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4:$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$7:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -3352,7 +3352,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$H$4:$H$7</c:f>
+              <c:f>'vente annuelle des produits '!$H$7:$H$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3382,7 +3382,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$I$3</c:f>
+              <c:f>'vente annuelle des produits '!$I$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3559,7 +3559,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4:$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$7:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -3579,7 +3579,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$I$4:$I$7</c:f>
+              <c:f>'vente annuelle des produits '!$I$7:$I$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3609,7 +3609,7 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$J$3</c:f>
+              <c:f>'vente annuelle des produits '!$J$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3786,7 +3786,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'vente annuelle des produits '!$A$4:$A$7</c:f>
+              <c:f>'vente annuelle des produits '!$A$7:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -3806,7 +3806,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'vente annuelle des produits '!$J$4:$J$7</c:f>
+              <c:f>'vente annuelle des produits '!$J$7:$J$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -5692,13 +5692,88 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>404091</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>36079</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF58756E-AEF5-4731-B35D-4FBB76C203BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2092614" cy="505113"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" b="1"/>
+            <a:t>MOGUANGUE</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" b="1" baseline="0"/>
+            <a:t> AUGUSTE Arcel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1050" b="1" baseline="0"/>
+            <a:t>Master 1 IG </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1050" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>448641</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5728,13 +5803,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>43848</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>986</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>540694</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>986</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5764,13 +5839,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>352011</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>89728</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>241576</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>165652</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6096,185 +6171,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0579E7C3-6796-4CFC-AFD6-1B1BD2BB3CA1}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A4:K11"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.26953125" customWidth="1"/>
+    <col min="1" max="1" width="7.08984375" customWidth="1"/>
     <col min="2" max="11" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22" x14ac:dyDescent="0.65">
-      <c r="D1" s="2" t="s">
+    <row r="4" spans="1:11" ht="22" x14ac:dyDescent="0.65">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="51" x14ac:dyDescent="0.35">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4" t="s">
+    <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="5"/>
+      <c r="K6" s="5"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B7" s="1">
         <v>11100</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C7" s="1">
         <v>22000</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D7" s="1">
         <v>50</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E7" s="1">
         <v>62356</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F7" s="1">
         <v>233623</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G7" s="1">
         <v>335656</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H7" s="1">
         <v>3236</v>
       </c>
-      <c r="I4" s="1">
-        <f>SUM(B4+C4+D4+E4+F4+G4+H4)</f>
+      <c r="I7" s="1">
+        <f>SUM(B7+C7+D7+E7+F7+G7+H7)</f>
         <v>668021</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f>IF(I4&gt;0,"gain","perte")</f>
-        <v>gain</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>10000</v>
-      </c>
-      <c r="C5" s="1">
-        <v>150000</v>
-      </c>
-      <c r="D5" s="1">
-        <v>600000</v>
-      </c>
-      <c r="E5" s="1">
-        <v>200000</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>152000</v>
-      </c>
-      <c r="H5" s="1">
-        <v>20000</v>
-      </c>
-      <c r="I5" s="1">
-        <f>SUM(B5+C5+D5+E5+F5+G5+H5)</f>
-        <v>1132000</v>
-      </c>
-      <c r="J5" s="1" t="str">
-        <f>IF(I5&gt;0,"gain","perte")</f>
-        <v>gain</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1">
-        <v>-200000</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2222</v>
-      </c>
-      <c r="D6" s="1">
-        <v>-70000</v>
-      </c>
-      <c r="E6" s="1">
-        <v>60000</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3000000</v>
-      </c>
-      <c r="G6" s="1">
-        <v>50000</v>
-      </c>
-      <c r="H6" s="1">
-        <v>-800000</v>
-      </c>
-      <c r="I6" s="1">
-        <v>-300000</v>
-      </c>
-      <c r="J6" s="1" t="str">
-        <f>IF(I6&gt;0,"gain","perte")</f>
-        <v>perte</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6">
-        <f t="shared" ref="B7:I7" si="0">SUM(B4+B5+B6)</f>
-        <v>-178900</v>
-      </c>
-      <c r="C7" s="6">
-        <f t="shared" si="0"/>
-        <v>174222</v>
-      </c>
-      <c r="D7" s="6">
-        <f t="shared" si="0"/>
-        <v>530050</v>
-      </c>
-      <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>322356</v>
-      </c>
-      <c r="F7" s="6">
-        <f t="shared" si="0"/>
-        <v>3233623</v>
-      </c>
-      <c r="G7" s="6">
-        <f t="shared" si="0"/>
-        <v>537656</v>
-      </c>
-      <c r="H7" s="6">
-        <f t="shared" si="0"/>
-        <v>-776764</v>
-      </c>
-      <c r="I7" s="6">
-        <f t="shared" si="0"/>
-        <v>1500021</v>
       </c>
       <c r="J7" s="1" t="str">
         <f>IF(I7&gt;0,"gain","perte")</f>
@@ -6282,20 +6249,128 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
+      <c r="A8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C8" s="1">
+        <v>150000</v>
+      </c>
+      <c r="D8" s="1">
+        <v>600000</v>
+      </c>
+      <c r="E8" s="1">
+        <v>200000</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>152000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20000</v>
+      </c>
+      <c r="I8" s="1">
+        <f>SUM(B8+C8+D8+E8+F8+G8+H8)</f>
+        <v>1132000</v>
+      </c>
+      <c r="J8" s="1" t="str">
+        <f>IF(I8&gt;0,"gain","perte")</f>
+        <v>gain</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-200000</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2222</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-70000</v>
+      </c>
+      <c r="E9" s="1">
+        <v>60000</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3000000</v>
+      </c>
+      <c r="G9" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H9" s="1">
+        <v>-800000</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-300000</v>
+      </c>
+      <c r="J9" s="1" t="str">
+        <f>IF(I9&gt;0,"gain","perte")</f>
+        <v>perte</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6">
+        <f t="shared" ref="B10:I10" si="0">SUM(B7+B8+B9)</f>
+        <v>-178900</v>
+      </c>
+      <c r="C10" s="6">
+        <f t="shared" si="0"/>
+        <v>174222</v>
+      </c>
+      <c r="D10" s="6">
+        <f t="shared" si="0"/>
+        <v>530050</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="shared" si="0"/>
+        <v>322356</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="0"/>
+        <v>3233623</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="0"/>
+        <v>537656</v>
+      </c>
+      <c r="H10" s="6">
+        <f t="shared" si="0"/>
+        <v>-776764</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="0"/>
+        <v>1500021</v>
+      </c>
+      <c r="J10" s="1" t="str">
+        <f>IF(I10&gt;0,"gain","perte")</f>
+        <v>gain</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="10"/>
     </row>
   </sheetData>
-  <sortState caseSensitive="1" ref="A4:I6">
-    <sortCondition descending="1" ref="I4:I6"/>
+  <sortState caseSensitive="1" ref="A7:I9">
+    <sortCondition descending="1" ref="I7:I9"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
